--- a/event_list.xlsx
+++ b/event_list.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
   <si>
     <t>date</t>
   </si>
@@ -35,15 +35,6 @@
   </si>
   <si>
     <t>details</t>
-  </si>
-  <si>
-    <t>day</t>
-  </si>
-  <si>
-    <t>month</t>
-  </si>
-  <si>
-    <t>year</t>
   </si>
   <si>
     <t>Colloquium</t>
@@ -64,20 +55,14 @@
 [View programme](events/programmes/workshop-name.pdf){.event-link}
 </t>
   </si>
-  <si>
-    <t>Course</t>
-  </si>
-  <si>
-    <t>Workshop</t>
-  </si>
-  <si>
-    <t>Talk</t>
-  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="[$-1070000]d/mm/yyyy;@"/>
+  </numFmts>
   <fonts count="3">
     <font>
       <sz val="10.000000"/>
@@ -122,15 +107,18 @@
     <xf fontId="1" fillId="0" borderId="0" numFmtId="9" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyProtection="0"/>
     <xf fontId="2" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyProtection="0">
       <protection hidden="0" locked="1"/>
     </xf>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1" applyProtection="0">
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="164" xfId="0" applyNumberFormat="1" applyProtection="0">
+      <protection hidden="0" locked="1"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="164" xfId="0" applyNumberFormat="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="top"/>
       <protection hidden="0" locked="1"/>
     </xf>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="14" xfId="0" applyNumberFormat="1" applyAlignment="1" applyProtection="0">
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1" applyProtection="0">
       <alignment vertical="top"/>
       <protection hidden="0" locked="1"/>
     </xf>
@@ -138,7 +126,7 @@
       <alignment vertical="top" wrapText="1"/>
       <protection hidden="0" locked="1"/>
     </xf>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="14" xfId="0" applyNumberFormat="1" applyAlignment="1" applyProtection="0">
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="164" xfId="0" applyNumberFormat="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="top"/>
       <protection hidden="0" locked="1"/>
     </xf>
@@ -619,394 +607,125 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
   <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="13.7109375"/>
+    <col customWidth="1" min="1" max="1" style="1" width="13.7109375"/>
     <col customWidth="1" min="6" max="6" width="90.00390625"/>
   </cols>
   <sheetData>
     <row r="1" ht="12.75">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+    </row>
+    <row r="2" ht="102">
+      <c r="A2" s="2">
+        <v>46377</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="C2" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="D2" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="2" ht="12.75">
-      <c r="A2" s="2">
-        <v>46699</v>
-      </c>
-      <c r="B2" s="1" t="s">
+      <c r="E2" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="F2" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="D2" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="G2" s="1">
-        <f>DAY(A2)</f>
+    </row>
+    <row r="3" ht="102">
+      <c r="A3" s="5">
+        <v>46290</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D3" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="H2" s="2" t="str">
-        <f>UPPER(TEXT(A2,"mmm"))</f>
-        <v>NOV</v>
-      </c>
-      <c r="I2" s="1">
-        <f>YEAR(A2)</f>
-        <v>2027</v>
-      </c>
-      <c r="J2"/>
-    </row>
-    <row r="3" ht="12.75">
-      <c r="A3" s="2">
-        <v>46560</v>
-      </c>
-      <c r="B3" s="1" t="s">
+      <c r="E3" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="F3" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="D3" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="G3" s="1">
-        <f>DAY(A3)</f>
-        <v>22</v>
-      </c>
-      <c r="H3" s="2" t="str">
-        <f>UPPER(TEXT(A3,"mmm"))</f>
-        <v>JUN</v>
-      </c>
-      <c r="I3" s="1">
-        <f>YEAR(A3)</f>
-        <v>2027</v>
-      </c>
-      <c r="J3"/>
-    </row>
-    <row r="4" ht="12.75">
+      <c r="G3"/>
+      <c r="H3"/>
+      <c r="I3"/>
+    </row>
+    <row r="4" ht="102">
       <c r="A4" s="2">
-        <v>46527</v>
-      </c>
-      <c r="B4" s="1" t="s">
+        <v>46185</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E4" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="F4" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="D4" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="G4" s="1">
-        <f>DAY(A4)</f>
-        <v>20</v>
-      </c>
-      <c r="H4" s="2" t="str">
-        <f>UPPER(TEXT(A4,"mmm"))</f>
-        <v>MAY</v>
-      </c>
-      <c r="I4" s="1">
-        <f>YEAR(A4)</f>
-        <v>2027</v>
-      </c>
-      <c r="J4"/>
-    </row>
-    <row r="5" ht="102">
-      <c r="A5" s="4">
-        <v>46353</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="G5" s="1">
-        <f>DAY(A5)</f>
-        <v>27</v>
-      </c>
-      <c r="H5" s="4" t="str">
-        <f>UPPER(TEXT(A5,"mmm"))</f>
-        <v>NOV</v>
-      </c>
-      <c r="I5" s="1">
-        <f>YEAR(A5)</f>
-        <v>2026</v>
-      </c>
-      <c r="J5"/>
-    </row>
-    <row r="6" ht="102">
-      <c r="A6" s="4">
-        <v>46326</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="G6" s="1">
-        <f t="shared" ref="G6:G12" si="0">DAY(A6)</f>
-        <v>31</v>
-      </c>
-      <c r="H6" s="4" t="str">
-        <f t="shared" ref="H6:H12" si="1">UPPER(TEXT(A6,"mmm"))</f>
-        <v>OCT</v>
-      </c>
-      <c r="I6" s="1">
-        <f t="shared" ref="I6:I12" si="2">YEAR(A6)</f>
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="7" ht="102">
-      <c r="A7" s="4">
-        <v>46322</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="G7" s="1">
-        <f t="shared" si="0"/>
-        <v>27</v>
-      </c>
-      <c r="H7" s="4" t="str">
-        <f t="shared" si="1"/>
-        <v>OCT</v>
-      </c>
-      <c r="I7" s="1">
-        <f t="shared" si="2"/>
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="8" ht="102">
-      <c r="A8" s="4">
-        <v>46283</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="G8" s="1">
-        <f t="shared" si="0"/>
-        <v>18</v>
-      </c>
-      <c r="H8" s="4" t="str">
-        <f t="shared" si="1"/>
-        <v>SEP</v>
-      </c>
-      <c r="I8" s="1">
-        <f t="shared" si="2"/>
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="9" ht="90" customHeight="1">
-      <c r="A9" s="4">
-        <v>46285</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="G9" s="1">
-        <f t="shared" si="0"/>
-        <v>20</v>
-      </c>
-      <c r="H9" s="4" t="str">
-        <f t="shared" si="1"/>
-        <v>SEP</v>
-      </c>
-      <c r="I9" s="1">
-        <f t="shared" si="2"/>
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="10" ht="102">
-      <c r="A10" s="4">
-        <v>45981</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="G10" s="1">
-        <f t="shared" si="0"/>
-        <v>20</v>
-      </c>
-      <c r="H10" s="4" t="str">
-        <f t="shared" si="1"/>
-        <v>NOV</v>
-      </c>
-      <c r="I10" s="1">
-        <f t="shared" si="2"/>
-        <v>2025</v>
-      </c>
-    </row>
-    <row r="11" ht="102">
-      <c r="A11" s="4">
-        <v>46078</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F11" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="G11" s="1">
-        <f t="shared" si="0"/>
-        <v>25</v>
-      </c>
-      <c r="H11" s="4" t="str">
-        <f t="shared" si="1"/>
-        <v>FEB</v>
-      </c>
-      <c r="I11" s="1">
-        <f t="shared" si="2"/>
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="12" ht="102">
-      <c r="A12" s="4">
-        <v>46174</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E12" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="G12" s="1">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="H12" s="4" t="str">
-        <f t="shared" si="1"/>
-        <v>JUN</v>
-      </c>
-      <c r="I12" s="1">
-        <f t="shared" si="2"/>
-        <v>2026</v>
-      </c>
+      <c r="G4"/>
+      <c r="H4"/>
+      <c r="I4"/>
+    </row>
+    <row r="5" ht="12.75">
+      <c r="A5" s="1"/>
+    </row>
+    <row r="6" ht="12.75">
+      <c r="A6" s="1"/>
+    </row>
+    <row r="7" ht="12.75">
+      <c r="A7" s="1"/>
+    </row>
+    <row r="8" ht="12.75">
+      <c r="A8" s="1"/>
+    </row>
+    <row r="9" ht="12.75">
+      <c r="A9" s="1"/>
+    </row>
+    <row r="10" ht="12.75">
+      <c r="A10" s="1"/>
+    </row>
+    <row r="11" ht="12.75">
+      <c r="A11" s="1"/>
+    </row>
+    <row r="12" ht="12.75">
+      <c r="A12" s="1"/>
+    </row>
+    <row r="13" ht="12.75">
+      <c r="A13" s="1"/>
+    </row>
+    <row r="14" ht="12.75">
+      <c r="A14" s="1"/>
     </row>
   </sheetData>
   <printOptions headings="0" gridLines="0"/>

--- a/event_list.xlsx
+++ b/event_list.xlsx
@@ -122,12 +122,12 @@
       <alignment vertical="top"/>
       <protection hidden="0" locked="1"/>
     </xf>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="164" xfId="0" applyNumberFormat="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="top"/>
+      <protection hidden="0" locked="1"/>
+    </xf>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1" applyProtection="0">
       <alignment vertical="top" wrapText="1"/>
-      <protection hidden="0" locked="1"/>
-    </xf>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="164" xfId="0" applyNumberFormat="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="top"/>
       <protection hidden="0" locked="1"/>
     </xf>
   </cellXfs>
@@ -632,8 +632,8 @@
       </c>
     </row>
     <row r="2" ht="102">
-      <c r="A2" s="2">
-        <v>46377</v>
+      <c r="A2" s="4">
+        <v>46306</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>6</v>
@@ -647,13 +647,16 @@
       <c r="E2" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="F2" s="4" t="s">
+      <c r="F2" s="5" t="s">
         <v>10</v>
       </c>
+      <c r="G2"/>
+      <c r="H2"/>
+      <c r="I2"/>
     </row>
     <row r="3" ht="102">
-      <c r="A3" s="5">
-        <v>46290</v>
+      <c r="A3" s="2">
+        <v>46054</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>6</v>
@@ -667,35 +670,15 @@
       <c r="E3" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="F3" s="4" t="s">
+      <c r="F3" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G3"/>
       <c r="H3"/>
       <c r="I3"/>
     </row>
-    <row r="4" ht="102">
-      <c r="A4" s="2">
-        <v>46185</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="G4"/>
-      <c r="H4"/>
-      <c r="I4"/>
+    <row r="4" ht="12.75">
+      <c r="A4" s="1"/>
     </row>
     <row r="5" ht="12.75">
       <c r="A5" s="1"/>
@@ -723,9 +706,6 @@
     </row>
     <row r="13" ht="12.75">
       <c r="A13" s="1"/>
-    </row>
-    <row r="14" ht="12.75">
-      <c r="A14" s="1"/>
     </row>
   </sheetData>
   <printOptions headings="0" gridLines="0"/>

--- a/event_list.xlsx
+++ b/event_list.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
   <si>
     <t>date</t>
   </si>
@@ -37,23 +37,43 @@
     <t>details</t>
   </si>
   <si>
-    <t>Colloquium</t>
-  </si>
-  <si>
-    <t xml:space="preserve">What even is redundancy and deficiency?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Name, Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">University of Vienna · University of Graz</t>
-  </si>
-  <si>
-    <t xml:space="preserve">**Time:** 09:00-17:00  
-**Location:** Seminar Room 14, University of Vienna
-This workshop examines the interaction between redundancy and deficiency across different linguistic domains.
-[View programme](events/programmes/workshop-name.pdf){.event-link}
-</t>
+    <t>Workshop</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Clitic Meeting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Anita Riedl</t>
+  </si>
+  <si>
+    <t xml:space="preserve">University of Salzburg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">**Date:** October 29-30&lt;br&gt;
+**Location:** University of Salzburg&lt;br&gt;
+&lt;br&gt;
+This workshop examines clitics.  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Current Issues in Syntax, Semantics, and Pragmatics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">**Date:** November 20-21&lt;br&gt;
+**Location:** University of Salzburg&lt;br&gt;
+&lt;br&gt;
+Fourth edition of the 'Current Issues in Syntax, Semantics, and Pragmatics' workshop&lt;br&gt;
+&lt;br&gt;
+Contact email: synsemprag.workshop@gmail.com&lt;br&gt;
+[Page of the conference](https://www.plus.ac.at/linguistik/tagungen-und-vortraege/tagungen/){.event-link}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SFB Retreat</t>
+  </si>
+  <si>
+    <t xml:space="preserve">**Date:** June 17-19&lt;br&gt;
+**Location:** Sport Hotel Kapfenberg&lt;br&gt;
+&lt;br&gt;
+Third edition of the SFB retreat.&lt;br&gt;</t>
   </si>
 </sst>
 </file>
@@ -107,7 +127,7 @@
     <xf fontId="1" fillId="0" borderId="0" numFmtId="9" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyProtection="0"/>
     <xf fontId="2" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyProtection="0">
       <protection hidden="0" locked="1"/>
     </xf>
@@ -123,6 +143,10 @@
       <protection hidden="0" locked="1"/>
     </xf>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="164" xfId="0" applyNumberFormat="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="top"/>
+      <protection hidden="0" locked="1"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1" applyProtection="0">
       <alignment vertical="top"/>
       <protection hidden="0" locked="1"/>
     </xf>
@@ -631,54 +655,54 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" ht="102">
+    <row r="2" ht="63.75">
       <c r="A2" s="4">
-        <v>46306</v>
-      </c>
-      <c r="B2" s="3" t="s">
+        <v>46324</v>
+      </c>
+      <c r="B2" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="D2" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="E2" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="F2" s="5" t="s">
+      <c r="F2" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="G2"/>
-      <c r="H2"/>
-      <c r="I2"/>
     </row>
     <row r="3" ht="102">
       <c r="A3" s="2">
-        <v>46054</v>
-      </c>
-      <c r="B3" s="3" t="s">
+        <v>46346</v>
+      </c>
+      <c r="B3" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>8</v>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="D3" s="3"/>
       <c r="E3" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="F3" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="G3"/>
-      <c r="H3"/>
-      <c r="I3"/>
-    </row>
-    <row r="4" ht="12.75">
-      <c r="A4" s="1"/>
+      <c r="F3" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4" ht="51">
+      <c r="A4" s="1">
+        <v>46190</v>
+      </c>
+      <c r="C4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F4" s="6" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="5" ht="12.75">
       <c r="A5" s="1"/>

--- a/event_list.xlsx
+++ b/event_list.xlsx
@@ -31,7 +31,7 @@
     <t>people</t>
   </si>
   <si>
-    <t>affiliation</t>
+    <t>location</t>
   </si>
   <si>
     <t>details</t>
@@ -43,37 +43,33 @@
     <t xml:space="preserve">Clitic Meeting</t>
   </si>
   <si>
-    <t xml:space="preserve">Anita Riedl</t>
-  </si>
-  <si>
     <t xml:space="preserve">University of Salzburg</t>
   </si>
   <si>
-    <t xml:space="preserve">**Date:** October 29-30&lt;br&gt;
-**Location:** University of Salzburg&lt;br&gt;
-&lt;br&gt;
-This workshop examines clitics.  </t>
+    <t xml:space="preserve">**Date:** October 29-30
+**Location:** University of Salzburg
+This workshop examines clitics.</t>
   </si>
   <si>
     <t xml:space="preserve">Current Issues in Syntax, Semantics, and Pragmatics</t>
   </si>
   <si>
-    <t xml:space="preserve">**Date:** November 20-21&lt;br&gt;
-**Location:** University of Salzburg&lt;br&gt;
-&lt;br&gt;
-Fourth edition of the 'Current Issues in Syntax, Semantics, and Pragmatics' workshop&lt;br&gt;
-&lt;br&gt;
-Contact email: synsemprag.workshop@gmail.com&lt;br&gt;
+    <t xml:space="preserve">**Date:** November 20-21
+**Location:** University of Salzburg
+Fourth edition of the 'Current Issues in Syntax, Semantics, and Pragmatics' workshop
+Contact email: synsemprag.workshop@gmail.com
 [Page of the conference](https://www.plus.ac.at/linguistik/tagungen-und-vortraege/tagungen/){.event-link}</t>
   </si>
   <si>
     <t xml:space="preserve">SFB Retreat</t>
   </si>
   <si>
-    <t xml:space="preserve">**Date:** June 17-19&lt;br&gt;
-**Location:** Sport Hotel Kapfenberg&lt;br&gt;
-&lt;br&gt;
-Third edition of the SFB retreat.&lt;br&gt;</t>
+    <t xml:space="preserve">Sport Hotel Kapfenberg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">**Date:** June 17-19
+**Location:** Sport Hotel Kapfenberg
+Third edition of the SFB retreat.</t>
   </si>
 </sst>
 </file>
@@ -83,7 +79,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="[$-1070000]d/mm/yyyy;@"/>
   </numFmts>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <sz val="10.000000"/>
       <color theme="1"/>
@@ -98,13 +94,25 @@
       <color theme="1"/>
       <name val="Calibri"/>
     </font>
+    <font>
+      <b/>
+      <sz val="10.000000"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
+        <bgColor theme="5" tint="0.79998168889431442"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -127,14 +135,32 @@
     <xf fontId="1" fillId="0" borderId="0" numFmtId="9" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyProtection="0"/>
     <xf fontId="2" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="11">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyProtection="0">
       <protection hidden="0" locked="1"/>
     </xf>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="164" xfId="0" applyNumberFormat="1" applyProtection="0">
-      <protection hidden="0" locked="1"/>
-    </xf>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="164" xfId="0" applyNumberFormat="1" applyAlignment="1" applyProtection="0">
+    <xf fontId="0" fillId="2" borderId="0" numFmtId="164" xfId="0" applyNumberFormat="1" applyFill="1" applyProtection="0">
+      <protection hidden="0" locked="1"/>
+    </xf>
+    <xf fontId="0" fillId="2" borderId="0" numFmtId="0" xfId="0" applyFill="1" applyProtection="0">
+      <protection hidden="0" locked="1"/>
+    </xf>
+    <xf fontId="3" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyProtection="0">
+      <protection hidden="0" locked="1"/>
+    </xf>
+    <xf fontId="3" fillId="2" borderId="0" numFmtId="164" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="top"/>
+      <protection hidden="0" locked="1"/>
+    </xf>
+    <xf fontId="3" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="top"/>
+      <protection hidden="0" locked="1"/>
+    </xf>
+    <xf fontId="3" fillId="2" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="top"/>
+      <protection hidden="0" locked="1"/>
+    </xf>
+    <xf fontId="0" fillId="2" borderId="0" numFmtId="164" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="top"/>
       <protection hidden="0" locked="1"/>
     </xf>
@@ -142,15 +168,11 @@
       <alignment vertical="top"/>
       <protection hidden="0" locked="1"/>
     </xf>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="164" xfId="0" applyNumberFormat="1" applyAlignment="1" applyProtection="0">
+    <xf fontId="0" fillId="2" borderId="0" numFmtId="0" xfId="0" applyFill="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="top"/>
       <protection hidden="0" locked="1"/>
     </xf>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1" applyProtection="0">
-      <alignment vertical="top"/>
-      <protection hidden="0" locked="1"/>
-    </xf>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1" applyProtection="0">
+    <xf fontId="0" fillId="2" borderId="0" numFmtId="0" xfId="0" applyFill="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="top" wrapText="1"/>
       <protection hidden="0" locked="1"/>
     </xf>
@@ -632,75 +654,80 @@
   <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
     <col customWidth="1" min="1" max="1" style="1" width="13.7109375"/>
-    <col customWidth="1" min="6" max="6" width="90.00390625"/>
+    <col customWidth="1" min="2" max="2" width="12.57421875"/>
+    <col customWidth="1" min="3" max="3" style="2" width="12.57421875"/>
+    <col customWidth="1" min="4" max="4" width="13.00390625"/>
+    <col bestFit="1" customWidth="1" min="5" max="5" width="20.140625"/>
+    <col customWidth="1" min="6" max="6" style="2" width="90.00390625"/>
   </cols>
   <sheetData>
-    <row r="1" ht="12.75">
-      <c r="A1" s="2" t="s">
+    <row r="1" s="3" customFormat="1" ht="12.75">
+      <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="6" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="2" ht="63.75">
-      <c r="A2" s="4">
+    <row r="2" ht="51">
+      <c r="A2" s="7">
         <v>46324</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="C2" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="D2" s="8"/>
+      <c r="E2" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="5" t="s">
+      <c r="F2" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="F2" s="6" t="s">
+    </row>
+    <row r="3" ht="89.25">
+      <c r="A3" s="7">
+        <v>46346</v>
+      </c>
+      <c r="B3" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" s="9" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="3" ht="102">
-      <c r="A3" s="2">
-        <v>46346</v>
-      </c>
-      <c r="B3" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C3" s="3" t="s">
+      <c r="D3" s="8"/>
+      <c r="E3" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="F3" s="10" t="s">
         <v>11</v>
-      </c>
-      <c r="D3" s="3"/>
-      <c r="E3" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="F3" s="6" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="4" ht="51">
       <c r="A4" s="1">
         <v>46190</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C4" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E4" t="s">
         <v>13</v>
       </c>
-      <c r="F4" s="6" t="s">
+      <c r="F4" s="10" t="s">
         <v>14</v>
       </c>
     </row>

--- a/event_list.xlsx
+++ b/event_list.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
   <si>
     <t>date</t>
   </si>
@@ -70,6 +70,20 @@
     <t xml:space="preserve">**Date:** June 17-19
 **Location:** Sport Hotel Kapfenberg
 Third edition of the SFB retreat.</t>
+  </si>
+  <si>
+    <t>Talk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">What is redundancy?</t>
+  </si>
+  <si>
+    <t>Edgar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">**Date:** October 30, 11:00-13:00
+Click [here](https://github.io/yanhiz/sfb_redefi){.event-link}
+</t>
   </si>
 </sst>
 </file>
@@ -135,7 +149,7 @@
     <xf fontId="1" fillId="0" borderId="0" numFmtId="9" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyProtection="0"/>
     <xf fontId="2" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="14">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyProtection="0">
       <protection hidden="0" locked="1"/>
     </xf>
@@ -174,6 +188,17 @@
     </xf>
     <xf fontId="0" fillId="2" borderId="0" numFmtId="0" xfId="0" applyFill="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="top" wrapText="1"/>
+      <protection hidden="0" locked="1"/>
+    </xf>
+    <xf fontId="0" fillId="2" borderId="0" numFmtId="0" xfId="0" applyFill="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="top" wrapText="1"/>
+      <protection hidden="0" locked="1"/>
+    </xf>
+    <xf fontId="0" fillId="2" borderId="0" numFmtId="164" xfId="0" applyNumberFormat="1" applyFill="1" applyProtection="0">
+      <protection hidden="0" locked="1"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1" applyProtection="0">
+      <alignment wrapText="1"/>
       <protection hidden="0" locked="1"/>
     </xf>
   </cellXfs>
@@ -713,7 +738,7 @@
       <c r="E3" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="F3" s="10" t="s">
+      <c r="F3" s="11" t="s">
         <v>11</v>
       </c>
     </row>
@@ -731,8 +756,25 @@
         <v>14</v>
       </c>
     </row>
-    <row r="5" ht="12.75">
-      <c r="A5" s="1"/>
+    <row r="5" ht="51">
+      <c r="A5" s="12">
+        <v>46325</v>
+      </c>
+      <c r="B5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C5" t="s">
+        <v>16</v>
+      </c>
+      <c r="D5" t="s">
+        <v>17</v>
+      </c>
+      <c r="E5" t="s">
+        <v>8</v>
+      </c>
+      <c r="F5" s="13" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="6" ht="12.75">
       <c r="A6" s="1"/>

--- a/event_list.xlsx
+++ b/event_list.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
   <si>
     <t>date</t>
   </si>
@@ -58,7 +58,7 @@
 **Location:** University of Salzburg
 Fourth edition of the 'Current Issues in Syntax, Semantics, and Pragmatics' workshop
 Contact email: synsemprag.workshop@gmail.com
-[Page of the conference](https://www.plus.ac.at/linguistik/tagungen-und-vortraege/tagungen/){.event-link}</t>
+[Page of the conference](https://www.plus.ac.at/linguistik/tagungen-und-vortraege/tagungen/)</t>
   </si>
   <si>
     <t xml:space="preserve">SFB Retreat</t>
@@ -70,20 +70,6 @@
     <t xml:space="preserve">**Date:** June 17-19
 **Location:** Sport Hotel Kapfenberg
 Third edition of the SFB retreat.</t>
-  </si>
-  <si>
-    <t>Talk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">What is redundancy?</t>
-  </si>
-  <si>
-    <t>Edgar</t>
-  </si>
-  <si>
-    <t xml:space="preserve">**Date:** October 30, 11:00-13:00
-Click [here](https://github.io/yanhiz/sfb_redefi){.event-link}
-</t>
   </si>
 </sst>
 </file>
@@ -149,7 +135,7 @@
     <xf fontId="1" fillId="0" borderId="0" numFmtId="9" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyProtection="0"/>
     <xf fontId="2" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="12">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyProtection="0">
       <protection hidden="0" locked="1"/>
     </xf>
@@ -192,13 +178,6 @@
     </xf>
     <xf fontId="0" fillId="2" borderId="0" numFmtId="0" xfId="0" applyFill="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="top" wrapText="1"/>
-      <protection hidden="0" locked="1"/>
-    </xf>
-    <xf fontId="0" fillId="2" borderId="0" numFmtId="164" xfId="0" applyNumberFormat="1" applyFill="1" applyProtection="0">
-      <protection hidden="0" locked="1"/>
-    </xf>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1" applyProtection="0">
-      <alignment wrapText="1"/>
       <protection hidden="0" locked="1"/>
     </xf>
   </cellXfs>
@@ -752,29 +731,14 @@
       <c r="E4" t="s">
         <v>13</v>
       </c>
-      <c r="F4" s="10" t="s">
+      <c r="F4" s="11" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="5" ht="51">
-      <c r="A5" s="12">
-        <v>46325</v>
-      </c>
-      <c r="B5" t="s">
-        <v>15</v>
-      </c>
-      <c r="C5" t="s">
-        <v>16</v>
-      </c>
-      <c r="D5" t="s">
-        <v>17</v>
-      </c>
-      <c r="E5" t="s">
-        <v>8</v>
-      </c>
-      <c r="F5" s="13" t="s">
-        <v>18</v>
-      </c>
+    <row r="5" ht="12.75">
+      <c r="A5" s="1"/>
+      <c r="C5"/>
+      <c r="F5"/>
     </row>
     <row r="6" ht="12.75">
       <c r="A6" s="1"/>
@@ -796,9 +760,6 @@
     </row>
     <row r="12" ht="12.75">
       <c r="A12" s="1"/>
-    </row>
-    <row r="13" ht="12.75">
-      <c r="A13" s="1"/>
     </row>
   </sheetData>
   <printOptions headings="0" gridLines="0"/>

--- a/event_list.xlsx
+++ b/event_list.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
   <si>
     <t>date</t>
   </si>
@@ -70,6 +70,19 @@
     <t xml:space="preserve">**Date:** June 17-19
 **Location:** Sport Hotel Kapfenberg
 Third edition of the SFB retreat.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Redundancy and Deficiency in Morphosyntactic Change</t>
+  </si>
+  <si>
+    <t xml:space="preserve">University of Iceland</t>
+  </si>
+  <si>
+    <t xml:space="preserve">**Date:** July 26-28, 2027
+**Location:** University of Iceland (Reykjavík)
+Workshop "W14 Redundancy and Deficiency in Morphosyntactic Change" organized by Dalina Kalluli, Ian Roberts and Charles Yang. The workshop is part of the 28th International Conference on Historical Linguistics (ICHL28).
+Call for papers: [online](https://ichl28.hi.is/call-for-papers/) and [pdf](/pdf/W14_Redundancy_and_Deficiency_in_Morphosyntactic_Change.pdf).
+</t>
   </si>
 </sst>
 </file>
@@ -101,7 +114,7 @@
       <name val="Arial"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -110,12 +123,18 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.79998168889431442"/>
-        <bgColor theme="5" tint="0.79998168889431442"/>
+        <fgColor theme="0" tint="0"/>
+        <bgColor theme="0" tint="0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0"/>
+        <bgColor theme="7" tint="0"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left style="none"/>
       <right style="none"/>
@@ -123,6 +142,21 @@
       <bottom style="none"/>
       <diagonal style="none"/>
     </border>
+    <border>
+      <left style="thin">
+        <color theme="0" tint="-0.14999847407452621"/>
+      </left>
+      <right style="thin">
+        <color theme="0" tint="-0.14999847407452621"/>
+      </right>
+      <top style="thin">
+        <color theme="0" tint="-0.14999847407452621"/>
+      </top>
+      <bottom style="thin">
+        <color theme="0" tint="-0.14999847407452621"/>
+      </bottom>
+      <diagonal style="none"/>
+    </border>
   </borders>
   <cellStyleXfs count="7">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
@@ -135,48 +169,44 @@
     <xf fontId="1" fillId="0" borderId="0" numFmtId="9" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyProtection="0"/>
     <xf fontId="2" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="11">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyProtection="0">
       <protection hidden="0" locked="1"/>
     </xf>
-    <xf fontId="0" fillId="2" borderId="0" numFmtId="164" xfId="0" applyNumberFormat="1" applyFill="1" applyProtection="0">
-      <protection hidden="0" locked="1"/>
-    </xf>
-    <xf fontId="0" fillId="2" borderId="0" numFmtId="0" xfId="0" applyFill="1" applyProtection="0">
-      <protection hidden="0" locked="1"/>
-    </xf>
-    <xf fontId="3" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyProtection="0">
-      <protection hidden="0" locked="1"/>
-    </xf>
-    <xf fontId="3" fillId="2" borderId="0" numFmtId="164" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="top"/>
-      <protection hidden="0" locked="1"/>
-    </xf>
-    <xf fontId="3" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="top"/>
-      <protection hidden="0" locked="1"/>
-    </xf>
-    <xf fontId="3" fillId="2" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="top"/>
-      <protection hidden="0" locked="1"/>
-    </xf>
-    <xf fontId="0" fillId="2" borderId="0" numFmtId="164" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="top"/>
-      <protection hidden="0" locked="1"/>
-    </xf>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1" applyProtection="0">
-      <alignment vertical="top"/>
-      <protection hidden="0" locked="1"/>
-    </xf>
-    <xf fontId="0" fillId="2" borderId="0" numFmtId="0" xfId="0" applyFill="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="top"/>
-      <protection hidden="0" locked="1"/>
-    </xf>
-    <xf fontId="0" fillId="2" borderId="0" numFmtId="0" xfId="0" applyFill="1" applyAlignment="1" applyProtection="0">
+    <xf fontId="0" fillId="2" borderId="1" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyProtection="0">
+      <protection hidden="0" locked="1"/>
+    </xf>
+    <xf fontId="0" fillId="2" borderId="1" numFmtId="164" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyProtection="0">
+      <protection hidden="0" locked="1"/>
+    </xf>
+    <xf fontId="3" fillId="2" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="0">
+      <protection hidden="0" locked="1"/>
+    </xf>
+    <xf fontId="3" fillId="3" borderId="1" numFmtId="164" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="top" wrapText="1"/>
       <protection hidden="0" locked="1"/>
     </xf>
-    <xf fontId="0" fillId="2" borderId="0" numFmtId="0" xfId="0" applyFill="1" applyAlignment="1" applyProtection="0">
+    <xf fontId="3" fillId="2" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="top" wrapText="1"/>
+      <protection hidden="0" locked="1"/>
+    </xf>
+    <xf fontId="3" fillId="3" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="top" wrapText="1"/>
+      <protection hidden="0" locked="1"/>
+    </xf>
+    <xf fontId="0" fillId="2" borderId="1" numFmtId="164" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="top" wrapText="1"/>
+      <protection hidden="0" locked="1"/>
+    </xf>
+    <xf fontId="0" fillId="2" borderId="1" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="top" wrapText="1"/>
+      <protection hidden="0" locked="1"/>
+    </xf>
+    <xf fontId="0" fillId="2" borderId="1" numFmtId="164" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="top" wrapText="1"/>
+      <protection hidden="0" locked="1"/>
+    </xf>
+    <xf fontId="0" fillId="2" borderId="1" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="top" wrapText="1"/>
       <protection hidden="0" locked="1"/>
     </xf>
@@ -657,12 +687,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
   <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
-    <col customWidth="1" min="1" max="1" style="1" width="13.7109375"/>
-    <col customWidth="1" min="2" max="2" width="12.57421875"/>
-    <col customWidth="1" min="3" max="3" style="2" width="12.57421875"/>
-    <col customWidth="1" min="4" max="4" width="13.00390625"/>
-    <col bestFit="1" customWidth="1" min="5" max="5" width="20.140625"/>
-    <col customWidth="1" min="6" max="6" style="2" width="90.00390625"/>
+    <col customWidth="1" min="1" max="1" style="2" width="13.7109375"/>
+    <col customWidth="1" min="2" max="2" style="1" width="12.57421875"/>
+    <col customWidth="1" min="3" max="3" style="1" width="22.421875"/>
+    <col customWidth="1" min="4" max="4" style="1" width="19.57421875"/>
+    <col customWidth="1" min="5" max="5" style="1" width="27.57421875"/>
+    <col customWidth="1" min="6" max="6" style="1" width="90.00390625"/>
+    <col min="7" max="16384" style="1" width="9.140625"/>
   </cols>
   <sheetData>
     <row r="1" s="3" customFormat="1" ht="12.75">
@@ -692,14 +723,14 @@
       <c r="B2" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="9" t="s">
+      <c r="C2" s="8" t="s">
         <v>7</v>
       </c>
       <c r="D2" s="8"/>
       <c r="E2" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="F2" s="10" t="s">
+      <c r="F2" s="8" t="s">
         <v>9</v>
       </c>
     </row>
@@ -710,56 +741,71 @@
       <c r="B3" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="9" t="s">
+      <c r="C3" s="8" t="s">
         <v>10</v>
       </c>
       <c r="D3" s="8"/>
       <c r="E3" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="F3" s="11" t="s">
+      <c r="F3" s="8" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="4" ht="51">
-      <c r="A4" s="1">
+      <c r="A4" s="7">
         <v>46190</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="B4" s="8"/>
+      <c r="C4" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="E4" t="s">
+      <c r="D4" s="8"/>
+      <c r="E4" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="F4" s="11" t="s">
+      <c r="F4" s="8" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="5" ht="12.75">
-      <c r="A5" s="1"/>
-      <c r="C5"/>
-      <c r="F5"/>
+    <row r="5" ht="140.25">
+      <c r="A5" s="9">
+        <v>46596</v>
+      </c>
+      <c r="B5" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="C5" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="D5" s="8"/>
+      <c r="E5" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="F5" s="10" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="6" ht="12.75">
-      <c r="A6" s="1"/>
+      <c r="A6" s="2"/>
     </row>
     <row r="7" ht="12.75">
-      <c r="A7" s="1"/>
+      <c r="A7" s="2"/>
     </row>
     <row r="8" ht="12.75">
-      <c r="A8" s="1"/>
+      <c r="A8" s="2"/>
     </row>
     <row r="9" ht="12.75">
-      <c r="A9" s="1"/>
+      <c r="A9" s="2"/>
     </row>
     <row r="10" ht="12.75">
-      <c r="A10" s="1"/>
+      <c r="A10" s="2"/>
     </row>
     <row r="11" ht="12.75">
-      <c r="A11" s="1"/>
+      <c r="A11" s="2"/>
     </row>
     <row r="12" ht="12.75">
-      <c r="A12" s="1"/>
+      <c r="A12" s="2"/>
     </row>
   </sheetData>
   <printOptions headings="0" gridLines="0"/>
